--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -153,7 +153,7 @@
     <t>0,80,15,5</t>
   </si>
   <si>
-    <t>Assets/03_Prefabs/Object/Mesh_WoodBox_Prefab.prefab</t>
+    <t>Assets/03_Prefabs/Object/Mesh_WoodBox_Prefab</t>
   </si>
   <si>
     <t>Object_03</t>
@@ -180,7 +180,7 @@
     <t>0, 10</t>
   </si>
   <si>
-    <t>Assets/03_Prefabs/Object/Mesh_IronBox_Prefab.prefab</t>
+    <t>Assets/03_Prefabs/Object/Mesh_IronBox_Prefab</t>
   </si>
   <si>
     <t>잠금해제금고</t>

--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="14568" windowHeight="8424"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -198,33 +214,197 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-    </font>
-    <font>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;\0022맑은 고딕\0022&quot;"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -238,9 +418,201 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
-    <border/>
+  <borders count="24">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
@@ -254,8 +626,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -265,8 +639,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -276,13 +652,19 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -292,6 +674,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -300,9 +683,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -317,17 +702,20 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -342,6 +730,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -350,30 +739,42 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -382,113 +783,570 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -678,30 +1536,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="7"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.38"/>
-    <col customWidth="1" min="3" max="3" width="19.25"/>
-    <col customWidth="1" min="4" max="4" width="14.38"/>
-    <col customWidth="1" min="5" max="5" width="14.25"/>
-    <col customWidth="1" min="6" max="6" width="18.38"/>
-    <col customWidth="1" min="7" max="7" width="20.25"/>
-    <col customWidth="1" min="8" max="8" width="23.0"/>
-    <col customWidth="1" min="9" max="9" width="19.88"/>
-    <col customWidth="1" min="10" max="10" width="26.5"/>
-    <col customWidth="1" min="11" max="11" width="17.25"/>
-    <col customWidth="1" min="12" max="13" width="15.38"/>
+    <col min="2" max="2" width="15.3796296296296" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="14.3796296296296" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="18.3796296296296" customWidth="1"/>
+    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="19.8796296296296" customWidth="1"/>
+    <col min="10" max="10" width="26.5" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="13" width="15.3796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,287 +1577,288 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="s">
+    <row r="2" customHeight="1" spans="1:13">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="s">
+    <row r="3" customHeight="1" spans="1:13">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="s">
+    <row r="4" customHeight="1" spans="1:13">
+      <c r="A4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19" t="s">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="18" t="s">
+      <c r="J4" s="19"/>
+      <c r="K4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="M4" s="20"/>
+      <c r="L4" s="17">
+        <v>1</v>
+      </c>
+      <c r="M4" s="19"/>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
+    <row r="5" customHeight="1" spans="1:13">
+      <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="23" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="M5" s="23" t="s">
+      <c r="L5" s="22">
+        <v>3</v>
+      </c>
+      <c r="M5" s="22" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="s">
+    <row r="6" customHeight="1" spans="1:13">
+      <c r="A6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="19" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="M6" s="23" t="s">
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22">
+        <v>5</v>
+      </c>
+      <c r="M6" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="s">
+    <row r="7" customHeight="1" spans="1:13">
+      <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19" t="s">
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="23" t="s">
+      <c r="J7" s="21"/>
+      <c r="K7" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="M7" s="23" t="s">
+      <c r="L7" s="22">
+        <v>5</v>
+      </c>
+      <c r="M7" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="s">
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="A8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19" t="s">
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="23" t="s">
+      <c r="J8" s="21"/>
+      <c r="K8" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="23">
-        <v>1.0</v>
-      </c>
-      <c r="M8" s="23" t="s">
+      <c r="L8" s="22">
+        <v>1</v>
+      </c>
+      <c r="M8" s="22" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -198,10 +198,28 @@
     <t>0,10,50,40</t>
   </si>
   <si>
+    <t>Mesh_BrokenIronBox_Prefab</t>
+  </si>
+  <si>
     <t>망가진 금고</t>
   </si>
   <si>
     <t>0,40,50,10</t>
+  </si>
+  <si>
+    <t>Object_06</t>
+  </si>
+  <si>
+    <t>다이얼 금고</t>
+  </si>
+  <si>
+    <t>금고다. 잠겨 있지 않지만 안에 좋은 아이템이 있다.</t>
+  </si>
+  <si>
+    <t>0,0,10,90</t>
+  </si>
+  <si>
+    <t>Mesh_Safe_Prefab</t>
   </si>
 </sst>
 </file>
@@ -969,7 +987,7 @@
         <v>5.0</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -977,7 +995,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>37</v>
@@ -1000,13 +1018,50 @@
         <v>39</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L8" s="20">
         <v>1.0</v>
       </c>
       <c r="M8" s="20" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -198,13 +198,13 @@
     <t>0,10,50,40</t>
   </si>
   <si>
+    <t>망가진 금고</t>
+  </si>
+  <si>
+    <t>0,40,50,10</t>
+  </si>
+  <si>
     <t>Mesh_BrokenIronBox_Prefab</t>
-  </si>
-  <si>
-    <t>망가진 금고</t>
-  </si>
-  <si>
-    <t>0,40,50,10</t>
   </si>
   <si>
     <t>Object_06</t>
@@ -987,7 +987,7 @@
         <v>5.0</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -995,7 +995,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>37</v>
@@ -1018,13 +1018,13 @@
         <v>39</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L8" s="20">
         <v>1.0</v>
       </c>
       <c r="M8" s="20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">

--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -198,13 +198,13 @@
     <t>0,10,50,40</t>
   </si>
   <si>
+    <t>망가진 금고</t>
+  </si>
+  <si>
+    <t>0,40,50,10</t>
+  </si>
+  <si>
     <t>Mesh_BrokenIronBox_Prefab</t>
-  </si>
-  <si>
-    <t>망가진 금고</t>
-  </si>
-  <si>
-    <t>0,40,50,10</t>
   </si>
   <si>
     <t>Object_06</t>
@@ -246,7 +246,7 @@
       <name val="&quot;\0022맑은 고딕\0022&quot;"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,6 +259,12 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border/>
@@ -419,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -488,6 +494,21 @@
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -987,7 +1008,7 @@
         <v>5.0</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -995,7 +1016,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>37</v>
@@ -1018,49 +1039,49 @@
         <v>39</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L8" s="20">
         <v>1.0</v>
       </c>
       <c r="M8" s="20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="20" t="s">
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="27">
         <v>1.0</v>
       </c>
-      <c r="M9" s="20" t="s">
+      <c r="M9" s="26" t="s">
         <v>67</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99A962D-8280-4358-86AA-C7E3C5DBCEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1620" yWindow="2250" windowWidth="25200" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
   <si>
     <t>데이터 Id</t>
   </si>
@@ -138,9 +147,6 @@
     <t>Item_Jewel_Diamond,Item_Jewel_Amethyst,Item_Jewel_Aquamarine,Item_Jewel_Emerald,Item_Jewel_Ruby,Item_Jewel_Sapphire,Item_Jewel_Topaz</t>
   </si>
   <si>
-    <t>100,0,0,0</t>
-  </si>
-  <si>
     <t>Mesh_Cabinet</t>
   </si>
   <si>
@@ -201,9 +207,6 @@
     <t>망가진 금고</t>
   </si>
   <si>
-    <t>0,40,50,10</t>
-  </si>
-  <si>
     <t>Mesh_BrokenIronBox_Prefab</t>
   </si>
   <si>
@@ -220,30 +223,62 @@
   </si>
   <si>
     <t>Mesh_Safe_Prefab</t>
+  </si>
+  <si>
+    <t>Item_Junk_Bottle_Blue,Item_Junk_Bottle_Pink_Large,Item_Junk_Can_Navy,Item_Junk_Fish,Item_Junk_Glasses,Item_Junk_Microphone,Item_Junk_Sculpture,Item_Junk_Stone</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>40,20,20,20</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,70,25,5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;\0022맑은 고딕\0022&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -251,7 +286,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -267,7 +302,13 @@
     </fill>
   </fills>
   <borders count="16">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
@@ -281,8 +322,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -292,8 +335,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -303,13 +348,19 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -319,6 +370,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -327,9 +379,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -344,17 +398,20 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -369,6 +426,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -377,30 +435,42 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -409,125 +479,76 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -717,30 +738,33 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.38"/>
-    <col customWidth="1" min="3" max="3" width="19.25"/>
-    <col customWidth="1" min="4" max="4" width="14.38"/>
-    <col customWidth="1" min="5" max="5" width="14.25"/>
-    <col customWidth="1" min="6" max="6" width="18.38"/>
-    <col customWidth="1" min="7" max="7" width="20.25"/>
-    <col customWidth="1" min="8" max="8" width="23.0"/>
-    <col customWidth="1" min="9" max="9" width="19.88"/>
-    <col customWidth="1" min="10" max="10" width="26.5"/>
-    <col customWidth="1" min="11" max="11" width="17.25"/>
-    <col customWidth="1" min="12" max="13" width="15.38"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="13" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,336 +780,337 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19" t="s">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="17">
+        <v>1</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>41</v>
+      <c r="K5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="19">
+        <v>3</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="17" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19">
+        <v>5</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19" t="s">
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J7" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="M5" s="20" t="s">
-        <v>47</v>
+      <c r="K7" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" s="19">
+        <v>5</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="21" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>57</v>
+      <c r="E8" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="19">
+        <v>1</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="21" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="20" t="s">
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22">
+        <v>0</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="23" t="s">
+      <c r="K9" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="23" t="s">
+      <c r="L9" s="24">
+        <v>1</v>
+      </c>
+      <c r="M9" s="23" t="s">
         <v>65</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="24">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="27">
-        <v>1.0</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99A962D-8280-4358-86AA-C7E3C5DBCEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D4F6AF-4BE6-4205-9121-0037CA92F406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="2250" windowWidth="25200" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1965" yWindow="2595" windowWidth="25200" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -144,24 +144,27 @@
     <t>0</t>
   </si>
   <si>
+    <t>Item_Junk_Bottle_Blue,Item_Junk_Bottle_Pink_Large,Item_Junk_Can_Navy,Item_Junk_Fish,Item_Junk_Glasses,Item_Junk_Microphone,Item_Junk_Sculpture,Item_Junk_Stone</t>
+  </si>
+  <si>
+    <t>Mesh_Cabinet</t>
+  </si>
+  <si>
+    <t>Object_02</t>
+  </si>
+  <si>
+    <t>나무상자</t>
+  </si>
+  <si>
+    <t>WoodBox</t>
+  </si>
+  <si>
+    <t>나무상자다. 주로 값 싼 보석이 들어있지만 가끔 좋은 보석이 나오는 경우도 있다.</t>
+  </si>
+  <si>
     <t>Item_Jewel_Diamond,Item_Jewel_Amethyst,Item_Jewel_Aquamarine,Item_Jewel_Emerald,Item_Jewel_Ruby,Item_Jewel_Sapphire,Item_Jewel_Topaz</t>
   </si>
   <si>
-    <t>Mesh_Cabinet</t>
-  </si>
-  <si>
-    <t>Object_02</t>
-  </si>
-  <si>
-    <t>나무상자</t>
-  </si>
-  <si>
-    <t>WoodBox</t>
-  </si>
-  <si>
-    <t>나무상자다. 주로 값 싼 보석이 들어있지만 가끔 좋은 보석이 나오는 경우도 있다.</t>
-  </si>
-  <si>
     <t>0,80,15,5</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
     <t>망가진 금고</t>
   </si>
   <si>
+    <t>0,70,25,5</t>
+  </si>
+  <si>
     <t>Mesh_BrokenIronBox_Prefab</t>
   </si>
   <si>
@@ -225,23 +231,15 @@
     <t>Mesh_Safe_Prefab</t>
   </si>
   <si>
-    <t>Item_Junk_Bottle_Blue,Item_Junk_Bottle_Pink_Large,Item_Junk_Can_Navy,Item_Junk_Fish,Item_Junk_Glasses,Item_Junk_Microphone,Item_Junk_Sculpture,Item_Junk_Stone</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>40,20,20,20</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,70,25,5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>60,0,20,20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -268,6 +266,13 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;\0022\\0022맑은 고딕\\0022\0022&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="3"/>
@@ -281,18 +286,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -500,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -516,20 +515,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -911,13 +910,13 @@
       <c r="I4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="L4" s="17">
+      <c r="J4" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="20">
         <v>1</v>
       </c>
       <c r="M4" s="17" t="s">
@@ -928,13 +927,13 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>44</v>
       </c>
       <c r="E5" s="16" t="s">
@@ -949,67 +948,67 @@
         <v>38</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="19">
+        <v>46</v>
+      </c>
+      <c r="L5" s="22">
         <v>3</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>50</v>
       </c>
+      <c r="D6" s="21" t="s">
+        <v>51</v>
+      </c>
       <c r="E6" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="19">
+      <c r="L6" s="22">
         <v>5</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>50</v>
+      <c r="D7" s="21" t="s">
+        <v>51</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>36</v>
@@ -1023,30 +1022,30 @@
         <v>38</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" s="19">
+        <v>59</v>
+      </c>
+      <c r="L7" s="22">
         <v>5</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>50</v>
+      <c r="D8" s="21" t="s">
+        <v>51</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>36</v>
@@ -1060,57 +1059,57 @@
         <v>38</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="19">
+        <v>45</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="22">
         <v>1</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>63</v>
+      <c r="D9" s="23" t="s">
+        <v>65</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22">
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="20">
         <v>0</v>
       </c>
-      <c r="J9" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="L9" s="24">
+      <c r="J9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="22">
         <v>1</v>
       </c>
-      <c r="M9" s="23" t="s">
-        <v>65</v>
+      <c r="M9" s="19" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/InteractableContainer.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableContainer.xlsx
@@ -1,21 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D4F6AF-4BE6-4205-9121-0037CA92F406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="1965" yWindow="2595" windowWidth="25200" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="시트1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -147,6 +138,9 @@
     <t>Item_Junk_Bottle_Blue,Item_Junk_Bottle_Pink_Large,Item_Junk_Can_Navy,Item_Junk_Fish,Item_Junk_Glasses,Item_Junk_Microphone,Item_Junk_Sculpture,Item_Junk_Stone</t>
   </si>
   <si>
+    <t>60,0,20,20</t>
+  </si>
+  <si>
     <t>Mesh_Cabinet</t>
   </si>
   <si>
@@ -229,61 +223,34 @@
   </si>
   <si>
     <t>Mesh_Safe_Prefab</t>
-  </si>
-  <si>
-    <t>60,0,20,20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;\0022맑은 고딕\0022&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;\0022\\0022맑은 고딕\\0022\0022&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -291,7 +258,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -301,13 +268,7 @@
     </fill>
   </fills>
   <borders count="16">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
@@ -321,10 +282,8 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -334,10 +293,8 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -347,19 +304,13 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+    </border>
+    <border>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -369,7 +320,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -378,11 +328,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -397,20 +345,17 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -425,7 +370,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -434,42 +378,30 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+    </border>
+    <border>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -478,76 +410,128 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="29">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -737,33 +721,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="26.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" customWidth="1"/>
-    <col min="12" max="13" width="15.42578125" customWidth="1"/>
+    <col customWidth="1" min="2" max="2" width="15.38"/>
+    <col customWidth="1" min="3" max="3" width="19.25"/>
+    <col customWidth="1" min="4" max="4" width="14.38"/>
+    <col customWidth="1" min="5" max="5" width="14.25"/>
+    <col customWidth="1" min="6" max="6" width="18.38"/>
+    <col customWidth="1" min="7" max="7" width="20.25"/>
+    <col customWidth="1" min="8" max="8" width="23.0"/>
+    <col customWidth="1" min="9" max="9" width="19.88"/>
+    <col customWidth="1" min="10" max="10" width="26.5"/>
+    <col customWidth="1" min="11" max="11" width="17.25"/>
+    <col customWidth="1" min="12" max="13" width="15.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,337 +760,336 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="6" t="s">
+    <row r="2">
+      <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="10" t="s">
+    <row r="3">
+      <c r="A3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="14" t="s">
+    <row r="4">
+      <c r="A4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="M9" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="L4" s="20">
-        <v>1</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="22">
-        <v>3</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="22">
-        <v>5</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="22">
-        <v>5</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="22">
-        <v>1</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="20">
-        <v>0</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="22">
-        <v>1</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>